--- a/Collections/EURO/Spain/#EURO#Spain#Regular#[1999-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Spain/#EURO#Spain#Regular#[1999-present]#circulation_quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Spain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD7E59C-CBB2-46DF-B658-5FE9B3A526FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52C7146-60B8-431D-AB31-2F3133F3F0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -46,6 +46,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -404,7 +407,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="216">
   <si>
     <t>Year</t>
   </si>
@@ -1006,6 +1009,54 @@
   </si>
   <si>
     <t>Subtype_3#Map_of_Europe</t>
+  </si>
+  <si>
+    <t>77.713.500</t>
+  </si>
+  <si>
+    <t>235.411.500</t>
+  </si>
+  <si>
+    <t>178.813.500</t>
+  </si>
+  <si>
+    <t>177.911.500</t>
+  </si>
+  <si>
+    <t>137.013.500</t>
+  </si>
+  <si>
+    <t>93.811.500</t>
+  </si>
+  <si>
+    <t>114.113.500</t>
+  </si>
+  <si>
+    <t>70.711.500</t>
+  </si>
+  <si>
+    <t>60.813.500</t>
+  </si>
+  <si>
+    <t>74.011.500</t>
+  </si>
+  <si>
+    <t>19.613.500</t>
+  </si>
+  <si>
+    <t>44.411.500</t>
+  </si>
+  <si>
+    <t>118.413.500</t>
+  </si>
+  <si>
+    <t>155.111.500</t>
+  </si>
+  <si>
+    <t>1.013.500</t>
+  </si>
+  <si>
+    <t>911.500</t>
   </si>
 </sst>
 </file>
@@ -1360,7 +1411,136 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="40">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1537,15 +1717,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1577,9 +1748,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="23" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="16" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1848,7 +2019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="5" customWidth="1"/>
@@ -1915,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="4" t="str">
-        <f>IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G3:G29" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -1939,7 +2110,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="4" t="str">
-        <f>IF(OR(AND(F4&gt;1,F4&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1963,7 +2134,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="4" t="str">
-        <f>IF(OR(AND(F5&gt;1,F5&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1987,7 +2158,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="4" t="str">
-        <f>IF(OR(AND(F6&gt;1,F6&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I6" s="6"/>
@@ -2012,7 +2183,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="4" t="str">
-        <f>IF(OR(AND(F7&gt;1,F7&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
       <c r="I7" s="6"/>
@@ -2037,7 +2208,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="4" t="str">
-        <f>IF(OR(AND(F8&gt;1,F8&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
@@ -2061,7 +2232,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="4" t="str">
-        <f>IF(OR(AND(F9&gt;1,F9&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
@@ -2085,7 +2256,7 @@
         <v>2</v>
       </c>
       <c r="G10" s="4" t="str">
-        <f>IF(OR(AND(F10&gt;1,F10&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
@@ -2109,7 +2280,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="4" t="str">
-        <f>IF(OR(AND(F11&gt;1,F11&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
@@ -2133,7 +2304,7 @@
         <v>3</v>
       </c>
       <c r="G12" s="4" t="str">
-        <f>IF(OR(AND(F12&gt;1,F12&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
@@ -2157,7 +2328,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="4" t="str">
-        <f>IF(OR(AND(F13&gt;1,F13&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2181,7 +2352,7 @@
         <v>2</v>
       </c>
       <c r="G14" s="4" t="str">
-        <f>IF(OR(AND(F14&gt;1,F14&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
@@ -2205,7 +2376,7 @@
         <v>2</v>
       </c>
       <c r="G15" s="4" t="str">
-        <f>IF(OR(AND(F15&gt;1,F15&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
@@ -2229,7 +2400,7 @@
         <v>3</v>
       </c>
       <c r="G16" s="4" t="str">
-        <f>IF(OR(AND(F16&gt;1,F16&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
@@ -2253,7 +2424,7 @@
         <v>2</v>
       </c>
       <c r="G17" s="4" t="str">
-        <f>IF(OR(AND(F17&gt;1,F17&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
@@ -2277,7 +2448,7 @@
         <v>2</v>
       </c>
       <c r="G18" s="4" t="str">
-        <f>IF(OR(AND(F18&gt;1,F18&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
@@ -2301,7 +2472,7 @@
         <v>2</v>
       </c>
       <c r="G19" s="4" t="str">
-        <f>IF(OR(AND(F19&gt;1,F19&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
@@ -2325,7 +2496,7 @@
         <v>3</v>
       </c>
       <c r="G20" s="4" t="str">
-        <f>IF(OR(AND(F20&gt;1,F20&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
@@ -2349,7 +2520,7 @@
         <v>5</v>
       </c>
       <c r="G21" s="4" t="str">
-        <f>IF(OR(AND(F21&gt;1,F21&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
@@ -2373,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="4" t="str">
-        <f>IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2397,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="4" t="str">
-        <f>IF(OR(AND(F23&gt;1,F23&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2421,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="4" t="str">
-        <f>IF(OR(AND(F24&gt;1,F24&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2445,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="4" t="str">
-        <f>IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2469,7 +2640,77 @@
         <v>0</v>
       </c>
       <c r="G26" s="4" t="str">
-        <f>IF(OR(AND(F26&gt;1,F26&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="11">
+        <v>2023</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="11">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="11">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="14"/>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="str">
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2481,11 +2722,45 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="F25 F3:F23">
-    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="39" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F23 F25">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24 F26">
+    <cfRule type="containsText" dxfId="38" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24 F26">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28">
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2497,12 +2772,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F26">
-    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F24))))</formula>
+  <conditionalFormatting sqref="F27 F29">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F26 F24">
+  <conditionalFormatting sqref="F27 F29">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2522,7 +2797,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="5" customWidth="1"/>
@@ -3109,7 +3384,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="4" t="str">
-        <f t="shared" ref="G25:G26" si="2">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G25:G27" si="2">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3134,6 +3409,76 @@
       </c>
       <c r="G26" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="11">
+        <v>2023</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="11">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4" t="str">
+        <f t="shared" ref="G28:G29" si="3">IF(OR(AND(F28&gt;1,F28&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="11">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="14"/>
+      <c r="F29" s="29">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3145,12 +3490,12 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="F3:F20">
-    <cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="37" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F20">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3162,11 +3507,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21:F26">
-    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21:F26">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27:F29">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27:F29">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3186,7 +3548,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="5" customWidth="1"/>
@@ -3775,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="4" t="str">
-        <f t="shared" ref="G25:G26" si="2">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G25:G27" si="2">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3800,6 +4162,76 @@
       </c>
       <c r="G26" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="11">
+        <v>2023</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="11">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4" t="str">
+        <f t="shared" ref="G28:G29" si="3">IF(OR(AND(F28&gt;1,F28&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="11">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="14"/>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3811,11 +4243,45 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="F3:F22">
-    <cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="35" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F22">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23 F25">
+    <cfRule type="containsText" dxfId="34" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23 F25">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24 F26">
+    <cfRule type="containsText" dxfId="33" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24 F26">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3827,12 +4293,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F25">
-    <cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
+  <conditionalFormatting sqref="F28">
+    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F25 F23">
+  <conditionalFormatting sqref="F28">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3844,12 +4310,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F26">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F24))))</formula>
+  <conditionalFormatting sqref="F27 F29">
+    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F26 F24">
+  <conditionalFormatting sqref="F27 F29">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3869,7 +4335,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="5" customWidth="1"/>
@@ -4564,7 +5030,86 @@
         <v>0</v>
       </c>
       <c r="H26" s="4" t="str">
-        <f t="shared" ref="H26" si="3">IF(OR(AND(G26&gt;1,G26&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="H26:H28" si="3">IF(OR(AND(G26&gt;1,G26&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="11">
+        <v>2023</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="11">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="11">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="str">
+        <f t="shared" ref="H29" si="4">IF(OR(AND(G29&gt;1,G29&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -4575,11 +5120,11 @@
     <mergeCell ref="C1:E1"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="G25 G23">
-    <cfRule type="containsText" dxfId="14" priority="13" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G23 G25">
+    <cfRule type="containsText" dxfId="32" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -4591,11 +5136,41 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24 G26">
+    <cfRule type="containsText" dxfId="30" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4607,9 +5182,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G26 G24">
-    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
+  <conditionalFormatting sqref="G27 G29">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -4630,7 +5205,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="5" customWidth="1"/>
@@ -5302,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="4" t="str">
-        <f t="shared" ref="H25:H26" si="1">IF(OR(AND(G25&gt;1,G25&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="H25:H27" si="1">IF(OR(AND(G25&gt;1,G25&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -5330,6 +5905,85 @@
       </c>
       <c r="H26" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="11">
+        <v>2023</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="11">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4" t="str">
+        <f t="shared" ref="H28:H29" si="2">IF(OR(AND(G28&gt;1,G28&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="11">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -5341,11 +5995,41 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G23 G25">
+    <cfRule type="containsText" dxfId="28" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24 G26">
+    <cfRule type="containsText" dxfId="27" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5357,9 +6041,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G25 G23">
-    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
+  <conditionalFormatting sqref="G28">
+    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -5372,9 +6056,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G26 G24">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
+  <conditionalFormatting sqref="G27 G29">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -5395,7 +6079,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="5" customWidth="1"/>
@@ -6065,7 +6749,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="4" t="str">
-        <f t="shared" ref="H25:H26" si="1">IF(OR(AND(G25&gt;1,G25&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="H25:H27" si="1">IF(OR(AND(G25&gt;1,G25&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -6093,6 +6777,85 @@
       </c>
       <c r="H26" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="11">
+        <v>2023</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="11">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4" t="str">
+        <f t="shared" ref="H28:H29" si="2">IF(OR(AND(G28&gt;1,G28&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="11">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -6104,12 +6867,12 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="26" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -6120,9 +6883,24 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G25 G23">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G23 G25">
+    <cfRule type="containsText" dxfId="25" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24 G26">
+    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -6135,9 +6913,24 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G26 G24">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
+  <conditionalFormatting sqref="G28">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27 G29">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -6158,7 +6951,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="5" customWidth="1"/>
@@ -6830,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="4" t="str">
-        <f t="shared" ref="H25:H26" si="1">IF(OR(AND(G25&gt;1,G25&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="H25:H27" si="1">IF(OR(AND(G25&gt;1,G25&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -6858,6 +7651,85 @@
       </c>
       <c r="H26" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="11">
+        <v>2023</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="11">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4" t="str">
+        <f t="shared" ref="H28:H29" si="2">IF(OR(AND(G28&gt;1,G28&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="11">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -6868,9 +7740,41 @@
     <mergeCell ref="C1:E1"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="G25 G23">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G23 G25">
+    <cfRule type="containsText" dxfId="23" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G22">
+    <cfRule type="containsText" dxfId="22" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G22">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24 G26">
+    <cfRule type="containsText" dxfId="21" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -6883,12 +7787,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G22">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+  <conditionalFormatting sqref="G28">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G22">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6900,9 +7802,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G26 G24">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
+  <conditionalFormatting sqref="G27 G29">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -6923,7 +7825,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:S29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="5" customWidth="1"/>
@@ -7641,16 +8543,70 @@
       <c r="E27" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="8"/>
+      <c r="F27" s="8" t="s">
+        <v>214</v>
+      </c>
       <c r="G27" s="3">
         <v>1</v>
       </c>
       <c r="H27" s="4" t="str">
-        <f t="shared" ref="H27" si="2">IF(OR(AND(G27&gt;1,G27&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="H27:H28" si="2">IF(OR(AND(G27&gt;1,G27&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
       <c r="R27" s="26"/>
       <c r="S27" s="26"/>
+    </row>
+    <row r="28" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="11">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="11">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="str">
+        <f t="shared" ref="H29" si="3">IF(OR(AND(G29&gt;1,G29&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="B2:F2" xr:uid="{00000000-0001-0000-0700-000000000000}"/>
@@ -7659,9 +8615,41 @@
     <mergeCell ref="C1:E1"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="G25 G23 G27">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G23 G25 G27">
+    <cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G22">
+    <cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G22">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24 G26">
+    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -7674,12 +8662,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G22">
+  <conditionalFormatting sqref="G29">
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G22">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7691,9 +8677,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G26 G24">
+  <conditionalFormatting sqref="G28">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>

--- a/Collections/EURO/Spain/#EURO#Spain#Regular#[1999-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Spain/#EURO#Spain#Regular#[1999-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Spain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52C7146-60B8-431D-AB31-2F3133F3F0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C12A9B-54B6-46C9-8483-60A58ADA3284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -1413,6 +1413,15 @@
   </cellStyles>
   <dxfs count="40">
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF9BE5FF"/>
@@ -1531,15 +1540,6 @@
           <bgColor rgb="FF9BE5FF"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -1748,9 +1748,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="16" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2743,7 +2743,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F24))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F26">
+  <conditionalFormatting sqref="F26 F24">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2756,7 +2756,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28">
-    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="37" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2773,11 +2773,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27 F29">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="36" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F27 F29">
+  <conditionalFormatting sqref="F29 F27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2885,7 +2885,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G4" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3490,7 +3490,7 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="F3:F20">
-    <cfRule type="containsText" dxfId="37" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="35" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3507,7 +3507,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21:F26">
-    <cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="34" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3524,7 +3524,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27:F29">
-    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3662,7 +3662,7 @@
         <v>71</v>
       </c>
       <c r="F5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3710,7 +3710,7 @@
         <v>73</v>
       </c>
       <c r="F7" s="29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="4" t="str">
         <f t="shared" si="0"/>
@@ -4243,7 +4243,7 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="F3:F22">
-    <cfRule type="containsText" dxfId="35" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4260,11 +4260,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23 F25">
-    <cfRule type="containsText" dxfId="34" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F25">
+  <conditionalFormatting sqref="F25 F23">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4277,11 +4277,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24 F26">
-    <cfRule type="containsText" dxfId="33" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F24))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F26">
+  <conditionalFormatting sqref="F26 F24">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4294,7 +4294,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28">
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4311,11 +4311,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27 F29">
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F27 F29">
+  <conditionalFormatting sqref="F29 F27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5120,8 +5120,8 @@
     <mergeCell ref="C1:E1"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="G23 G25">
-    <cfRule type="containsText" dxfId="32" priority="17" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G25 G23">
+    <cfRule type="containsText" dxfId="27" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="18">
@@ -5136,7 +5136,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="containsText" dxfId="31" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="26" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5152,8 +5152,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G24 G26">
-    <cfRule type="containsText" dxfId="30" priority="5" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G26 G24">
+    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -5168,7 +5168,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="24" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -5182,8 +5182,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G27 G29">
-    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G29 G27">
+    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -5995,7 +5995,7 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="containsText" dxfId="29" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6011,8 +6011,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23 G25">
-    <cfRule type="containsText" dxfId="28" priority="7" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G25 G23">
+    <cfRule type="containsText" dxfId="21" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -6026,8 +6026,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G24 G26">
-    <cfRule type="containsText" dxfId="27" priority="5" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G26 G24">
+    <cfRule type="containsText" dxfId="20" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -6042,7 +6042,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="19" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -6056,8 +6056,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G27 G29">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G29 G27">
+    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -6867,7 +6867,7 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="containsText" dxfId="26" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6883,8 +6883,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23 G25">
-    <cfRule type="containsText" dxfId="25" priority="9" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G25 G23">
+    <cfRule type="containsText" dxfId="16" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="10">
@@ -6898,8 +6898,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G24 G26">
-    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G26 G24">
+    <cfRule type="containsText" dxfId="15" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -6914,7 +6914,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -6928,8 +6928,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G27 G29">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G29 G27">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -7740,8 +7740,8 @@
     <mergeCell ref="C1:E1"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="G23 G25">
-    <cfRule type="containsText" dxfId="23" priority="9" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G25 G23">
+    <cfRule type="containsText" dxfId="12" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="10">
@@ -7756,7 +7756,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="containsText" dxfId="22" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7772,8 +7772,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G24 G26">
-    <cfRule type="containsText" dxfId="21" priority="5" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G26 G24">
+    <cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -7788,7 +7788,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -7802,8 +7802,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G27 G29">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G29 G27">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -8615,8 +8615,8 @@
     <mergeCell ref="C1:E1"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="G23 G25 G27">
-    <cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G25 G23 G27">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="10">
@@ -8631,7 +8631,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8647,8 +8647,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G24 G26">
-    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G26 G24">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -8663,7 +8663,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G29">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -8678,7 +8678,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
